--- a/artfynd/A 25482-2026 artfynd.xlsx
+++ b/artfynd/A 25482-2026 artfynd.xlsx
@@ -675,37 +675,32 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>118375515</v>
+        <v>118375514</v>
       </c>
       <c r="B2" t="n">
-        <v>79574</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,13 +710,13 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>520101</v>
+        <v>520050</v>
       </c>
       <c r="R2" t="n">
-        <v>6995679</v>
+        <v>6995516</v>
       </c>
       <c r="S2" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -777,37 +772,32 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>118375518</v>
+        <v>118375516</v>
       </c>
       <c r="B3" t="n">
-        <v>79111</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,13 +807,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>519981</v>
+        <v>520076</v>
       </c>
       <c r="R3" t="n">
-        <v>6995926</v>
+        <v>6995870</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -879,53 +869,48 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>118375519</v>
+        <v>121433752</v>
       </c>
       <c r="B4" t="n">
-        <v>79574</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Boggsjöhöjden, Jmt</t>
+          <t>Gårdstjärnhöjden, Gårdstjärnhöjden, Jmt</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>519974</v>
+        <v>520178</v>
       </c>
       <c r="R4" t="n">
         <v>6995965</v>
       </c>
       <c r="S4" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -949,12 +934,22 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2024-07-06</t>
+          <t>2024-12-02</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>11:16</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2024-07-06</t>
+          <t>2024-12-02</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>11:16</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -969,27 +964,22 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Anton Björk</t>
+          <t>Jenny Persson</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Anton Björk</t>
+          <t>Jenny Persson</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>118375517</v>
+        <v>118375518</v>
       </c>
       <c r="B5" t="n">
-        <v>79082</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79946</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -997,21 +987,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>229821</v>
+        <v>6453</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1021,10 +1011,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>520084</v>
+        <v>519981</v>
       </c>
       <c r="R5" t="n">
-        <v>6995852</v>
+        <v>6995926</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1083,15 +1073,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>118375516</v>
+        <v>118375515</v>
       </c>
       <c r="B6" t="n">
-        <v>78493</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1099,21 +1084,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1123,10 +1108,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>520076</v>
+        <v>520101</v>
       </c>
       <c r="R6" t="n">
-        <v>6995870</v>
+        <v>6995679</v>
       </c>
       <c r="S6" t="n">
         <v>25</v>
@@ -1185,15 +1170,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>118375514</v>
+        <v>118375519</v>
       </c>
       <c r="B7" t="n">
-        <v>78493</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1201,21 +1181,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1225,13 +1205,13 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>520050</v>
+        <v>519974</v>
       </c>
       <c r="R7" t="n">
-        <v>6995516</v>
+        <v>6995965</v>
       </c>
       <c r="S7" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1287,15 +1267,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121433752</v>
+        <v>118375517</v>
       </c>
       <c r="B8" t="n">
-        <v>78616</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79917</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1303,37 +1278,37 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>229821</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Gårdstjärnhöjden, Gårdstjärnhöjden, Jmt</t>
+          <t>Boggsjöhöjden, Jmt</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>520178</v>
+        <v>520084</v>
       </c>
       <c r="R8" t="n">
-        <v>6995965</v>
+        <v>6995852</v>
       </c>
       <c r="S8" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1357,22 +1332,12 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2024-12-02</t>
-        </is>
-      </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>11:16</t>
+          <t>2024-07-06</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2024-12-02</t>
-        </is>
-      </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>11:16</t>
+          <t>2024-07-06</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1387,12 +1352,12 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Jenny Persson</t>
+          <t>Anton Björk</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Jenny Persson</t>
+          <t>Anton Björk</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>

--- a/artfynd/A 25482-2026 artfynd.xlsx
+++ b/artfynd/A 25482-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY8"/>
+  <dimension ref="A1:AZ8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -769,6 +774,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118375514</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -866,6 +876,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118375516</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -973,6 +988,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121433752</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1070,6 +1090,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118375518</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1167,6 +1192,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118375515</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1264,6 +1294,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118375519</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1361,8 +1396,22 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118375517</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>